--- a/data/trans_bre/P57_AC_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P57_AC_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 14,95</t>
+          <t>3,63; 15,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 16,19</t>
+          <t>0,49; 15,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,75</t>
+          <t>-5,48; 8,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 15,24</t>
+          <t>-2,64; 14,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 19,45</t>
+          <t>4,34; 20,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 24,14</t>
+          <t>0,62; 22,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 9,84</t>
+          <t>-6,45; 10,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 33,33</t>
+          <t>-4,5; 31,65</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 14,15</t>
+          <t>1,35; 13,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 8,43</t>
+          <t>-3,63; 8,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 5,72</t>
+          <t>-3,95; 5,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 1,9</t>
+          <t>-12,97; 0,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 25,48</t>
+          <t>1,95; 25,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 16,25</t>
+          <t>-6,13; 16,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 7,46</t>
+          <t>-4,77; 7,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 3,18</t>
+          <t>-19,11; 1,19</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 2,86</t>
+          <t>-13,29; 3,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 16,3</t>
+          <t>2,39; 15,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 16,39</t>
+          <t>2,56; 16,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 12,44</t>
+          <t>-1,43; 13,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 5,57</t>
+          <t>-20,32; 5,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 27,18</t>
+          <t>3,55; 26,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 24,75</t>
+          <t>3,38; 23,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 30,35</t>
+          <t>-2,99; 33,47</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 5,51</t>
+          <t>-8,31; 5,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 16,28</t>
+          <t>2,93; 16,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 15,45</t>
+          <t>1,06; 16,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 6,5</t>
+          <t>-15,49; 6,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 8,34</t>
+          <t>-11,3; 8,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 34,57</t>
+          <t>5,35; 35,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 36,29</t>
+          <t>2,13; 39,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,84; 22,09</t>
+          <t>-43,33; 21,66</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 14,06</t>
+          <t>0,18; 15,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 28,34</t>
+          <t>8,39; 28,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 7,4</t>
+          <t>-5,13; 7,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 5,06</t>
+          <t>-4,93; 5,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 18,98</t>
+          <t>0,33; 20,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,76; 60,23</t>
+          <t>14,46; 59,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 8,91</t>
+          <t>-5,82; 8,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 5,63</t>
+          <t>-5,16; 5,85</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 12,33</t>
+          <t>-2,55; 12,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,8; 23,29</t>
+          <t>6,72; 22,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 7,04</t>
+          <t>-7,54; 6,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 8,58</t>
+          <t>-6,45; 8,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 18,61</t>
+          <t>-3,42; 18,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,82; 41,81</t>
+          <t>10,06; 39,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 9,55</t>
+          <t>-9,37; 9,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 24,64</t>
+          <t>-15,05; 23,66</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 2,49</t>
+          <t>-9,1; 2,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,81</t>
+          <t>3,93; 14,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 7,96</t>
+          <t>-1,09; 7,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 8,15</t>
+          <t>-4,28; 7,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 4,85</t>
+          <t>-16,45; 4,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 26,52</t>
+          <t>6,3; 25,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 10,05</t>
+          <t>-1,25; 9,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 14,25</t>
+          <t>-6,56; 13,58</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 9,81</t>
+          <t>2,19; 10,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,27</t>
+          <t>-3,88; 2,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,98</t>
+          <t>-1,66; 3,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 59,35</t>
+          <t>1,91; 59,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,86; 12,64</t>
+          <t>2,79; 13,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 2,57</t>
+          <t>-4,27; 2,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,38</t>
+          <t>-1,82; 4,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,01; 212,53</t>
+          <t>2,38; 213,69</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,21</t>
+          <t>0,45; 5,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,8</t>
+          <t>4,52; 8,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,86</t>
+          <t>1,1; 5,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 16,63</t>
+          <t>-1,63; 19,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,84</t>
+          <t>0,64; 7,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,49</t>
+          <t>6,66; 13,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,21</t>
+          <t>1,37; 6,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 37,78</t>
+          <t>-2,66; 44,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_AC_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P57_AC_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>5,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 15,33</t>
+          <t>4,03; 15,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 15,37</t>
+          <t>1,56; 15,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 8,08</t>
+          <t>-4,81; 8,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 14,69</t>
+          <t>-1,73; 13,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 20,04</t>
+          <t>4,79; 20,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 22,37</t>
+          <t>2,24; 22,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 10,22</t>
+          <t>-5,71; 10,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 31,65</t>
+          <t>-2,98; 26,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,03</t>
+          <t>-5,71</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-9,52%</t>
+          <t>-9,02%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,88</t>
+          <t>1,43; 13,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 8,68</t>
+          <t>-4,51; 8,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 5,96</t>
+          <t>-4,58; 5,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 0,92</t>
+          <t>-12,01; 0,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 25,18</t>
+          <t>2,24; 25,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 16,8</t>
+          <t>-7,68; 16,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 7,85</t>
+          <t>-5,52; 7,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 1,19</t>
+          <t>-18,16; 1,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>6,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 3,16</t>
+          <t>-11,94; 3,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 15,73</t>
+          <t>1,33; 15,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 16,0</t>
+          <t>2,97; 16,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 13,24</t>
+          <t>-1,25; 13,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 5,47</t>
+          <t>-18,62; 6,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 26,51</t>
+          <t>1,8; 25,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 23,66</t>
+          <t>4,04; 24,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 33,47</t>
+          <t>-2,24; 32,27</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,6</t>
+          <t>3,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-11,17%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 5,44</t>
+          <t>-9,08; 5,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 16,83</t>
+          <t>1,21; 16,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 16,33</t>
+          <t>0,9; 16,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 6,53</t>
+          <t>-4,66; 11,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 8,16</t>
+          <t>-12,09; 7,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 35,36</t>
+          <t>1,87; 33,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 39,26</t>
+          <t>1,78; 39,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,33; 21,66</t>
+          <t>-12,19; 39,48</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 15,3</t>
+          <t>-0,69; 14,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 28,27</t>
+          <t>9,21; 27,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 7,19</t>
+          <t>-5,57; 7,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 5,21</t>
+          <t>-3,61; 6,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 20,64</t>
+          <t>-0,8; 20,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 59,87</t>
+          <t>15,69; 58,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 8,67</t>
+          <t>-6,24; 8,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 5,85</t>
+          <t>-3,85; 7,05</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 12,09</t>
+          <t>-3,06; 11,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,72; 22,3</t>
+          <t>6,58; 22,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 6,98</t>
+          <t>-8,38; 6,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 8,22</t>
+          <t>-7,02; 7,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 18,38</t>
+          <t>-4,46; 18,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,06; 39,35</t>
+          <t>9,73; 38,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 9,57</t>
+          <t>-10,3; 8,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 23,66</t>
+          <t>-15,85; 19,67</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 2,08</t>
+          <t>-9,35; 1,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 14,55</t>
+          <t>3,53; 14,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 7,43</t>
+          <t>-0,7; 7,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 7,82</t>
+          <t>-3,88; 6,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 4,25</t>
+          <t>-16,94; 3,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 25,88</t>
+          <t>5,61; 24,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 9,38</t>
+          <t>-0,83; 9,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 13,58</t>
+          <t>-5,88; 11,74</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25,06</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 10,03</t>
+          <t>2,01; 9,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,29</t>
+          <t>-3,96; 2,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,76</t>
+          <t>-1,38; 3,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 59,02</t>
+          <t>-1,39; 6,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 13,01</t>
+          <t>2,43; 12,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 2,64</t>
+          <t>-4,37; 2,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,15</t>
+          <t>-1,48; 4,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 213,69</t>
+          <t>-1,56; 7,32</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,05</t>
+          <t>0,62; 5,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,92</t>
+          <t>4,74; 9,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,1</t>
+          <t>1,26; 4,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 19,23</t>
+          <t>-0,74; 4,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 7,51</t>
+          <t>0,91; 7,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,62</t>
+          <t>6,96; 13,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,56</t>
+          <t>1,57; 6,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 44,02</t>
+          <t>-1,13; 6,71</t>
         </is>
       </c>
     </row>
